--- a/documentacao/matrizes/Matriz_PLI_v6_Dimensoes_Indicadores.xlsx
+++ b/documentacao/matrizes/Matriz_PLI_v6_Dimensoes_Indicadores.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dimensões de Critérios'!$A$1:$C$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Critérios'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Matriz Crit Premissas v3'!$A$1:$N$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Notas de preenchimento'!$A$1:$B$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Notas de preenchimento'!$A$1:$B$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Rastreabilidade PLI'!$A$1:$I$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Fonte PLI v6'!$A$1:$B$156</definedName>
   </definedNames>
@@ -726,7 +726,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D1 · Técnica e logística</t>
+          <t>D1 · Eficiência logística</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>D1 · Técnica e logística</t>
+          <t>D1 · Eficiência logística</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Dimensão original do PLI; bloco: Mérito e resultados. Fonte: PLI_Fig_Estrutura_Criterios_v6.pptx, slide 1.</t>
+          <t>Dimensão do PLI; nome original: D1 · Técnica e logística; bloco: Mérito e resultados. Fonte: PLI_Fig_Estrutura_Criterios_v6.pptx, slide 1.</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Dimensão original do PLI; bloco: Mérito e resultados. Fonte: PLI_Fig_Estrutura_Criterios_v6.pptx, slide 1.</t>
+          <t>Dimensão do PLI; nome original: D2 · Econômica; bloco: Mérito e resultados. Fonte: PLI_Fig_Estrutura_Criterios_v6.pptx, slide 1.</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Dimensão original do PLI; bloco: Sustentabilidade e território. Fonte: PLI_Fig_Estrutura_Criterios_v6.pptx, slide 1.</t>
+          <t>Dimensão do PLI; nome original: D3 · Social e territorial; bloco: Sustentabilidade e território. Fonte: PLI_Fig_Estrutura_Criterios_v6.pptx, slide 1.</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Dimensão original do PLI; bloco: Sustentabilidade e território. Fonte: PLI_Fig_Estrutura_Criterios_v6.pptx, slide 1.</t>
+          <t>Dimensão do PLI; nome original: D4 · Segurança; bloco: Sustentabilidade e território. Fonte: PLI_Fig_Estrutura_Criterios_v6.pptx, slide 1.</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Dimensão original do PLI; bloco: Sustentabilidade e território. Fonte: PLI_Fig_Estrutura_Criterios_v6.pptx, slide 1.</t>
+          <t>Dimensão do PLI; nome original: D5 · Ambiental e climática; bloco: Sustentabilidade e território. Fonte: PLI_Fig_Estrutura_Criterios_v6.pptx, slide 1.</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Dimensão original do PLI; bloco: Capacidade de entrega. Fonte: PLI_Fig_Estrutura_Criterios_v6.pptx, slide 1.</t>
+          <t>Dimensão do PLI; nome original: D6 · Viabilidade institucional e financeira; bloco: Capacidade de entrega. Fonte: PLI_Fig_Estrutura_Criterios_v6.pptx, slide 1.</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Dimensão original do PLI; bloco: Capacidade de entrega. Fonte: PLI_Fig_Estrutura_Criterios_v6.pptx, slide 1.</t>
+          <t>Dimensão do PLI; nome original: D7 · Riscos; bloco: Capacidade de entrega. Fonte: PLI_Fig_Estrutura_Criterios_v6.pptx, slide 1.</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>D1 · Técnica e logística</t>
+          <t>D1 · Eficiência logística</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>D1 · Técnica e logística</t>
+          <t>D1 · Eficiência logística</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>D1 · Técnica e logística</t>
+          <t>D1 · Eficiência logística</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
     <row r="2" ht="135" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>D1 · Técnica e logística</t>
+          <t>D1 · Eficiência logística</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1472,7 +1472,7 @@
     <row r="3" ht="135" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>D1 · Técnica e logística</t>
+          <t>D1 · Eficiência logística</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -1544,7 +1544,7 @@
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>D1 · Técnica e logística</t>
+          <t>D1 · Eficiência logística</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2653,7 +2653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2891,17 +2891,29 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
+          <t>Nomenclatura D1</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Por solicitação do usuário, D1 · Técnica e logística passa a D1 · Eficiência logística nos campos operacionais. O nome original permanece nas abas Fonte PLI v6 e Rastreabilidade PLI. Fases, indicadores e regras não foram alterados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
           <t>Transcrição</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>A aba Fonte PLI v6 transcreve todos os textos dos dois slides, incluindo a meta e os objetivos estratégicos. Não foram utilizadas fontes normativas externas.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B20"/>
+  <autoFilter ref="A1:B21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
